--- a/models/orgtypes.xlsx
+++ b/models/orgtypes.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5EA169-CAC7-6547-984E-E934114E42FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BB2E74-0D34-484E-8164-42F8738A82FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="10220" windowWidth="27040" windowHeight="15760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="10220" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
     <sheet name="fields" sheetId="2" r:id="rId2"/>
     <sheet name="validation" sheetId="3" r:id="rId3"/>
-    <sheet name="codes" sheetId="6" r:id="rId4"/>
-    <sheet name="coding" sheetId="4" r:id="rId5"/>
-    <sheet name="help" sheetId="5" r:id="rId6"/>
+    <sheet name="data" sheetId="7" r:id="rId4"/>
+    <sheet name="codes" sheetId="6" r:id="rId5"/>
+    <sheet name="coding" sheetId="4" r:id="rId6"/>
+    <sheet name="help" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t>name</t>
   </si>
@@ -268,37 +269,56 @@
   </si>
   <si>
     <t>parentid='org_type'</t>
+  </si>
+  <si>
+    <t>orgtypes-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>owner</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>orgtypes-2</t>
+  </si>
+  <si>
+    <t>reseller</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -306,7 +326,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -366,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -399,9 +419,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -675,13 +698,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
     <col min="2" max="3" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -695,7 +718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
         <v>72</v>
       </c>
@@ -727,7 +750,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
@@ -736,7 +759,7 @@
     <col min="13" max="13" width="83" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -776,7 +799,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="9" t="s">
         <v>74</v>
       </c>
@@ -790,7 +813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" s="9" t="s">
         <v>76</v>
       </c>
@@ -804,25 +827,25 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="B5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="B6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="B7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="B9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="B10" s="8"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="B11" s="8"/>
     </row>
   </sheetData>
@@ -847,12 +870,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -863,16 +886,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="7"/>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="C6" s="5"/>
     </row>
   </sheetData>
@@ -906,55 +929,100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8295B5-7B2C-D34D-A853-65063EEB9A26}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABDE720-EE2F-E74A-8A08-A1324FD8BEC9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>37</v>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>66</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>80</v>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8295B5-7B2C-D34D-A853-65063EEB9A26}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -968,7 +1036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -982,7 +1050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -996,7 +1064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1007,7 +1075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1015,7 +1083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1023,7 +1091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1031,7 +1099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1039,7 +1107,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1047,7 +1115,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1055,17 +1123,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -1077,10 +1145,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.1640625" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1089,7 +1157,7 @@
     <col min="5" max="5" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="11" t="s">
         <v>42</v>
       </c>
@@ -1102,7 +1170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1119,7 +1187,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1134,7 +1202,7 @@
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1149,7 +1217,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -1164,7 +1232,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1179,7 +1247,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1194,7 +1262,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1209,7 +1277,7 @@
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -1220,7 +1288,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
@@ -1231,7 +1299,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
@@ -1242,7 +1310,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
